--- a/erp-server/erp-server-oms/src/main/resources/excel/SalesContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SalesContract.xlsx
@@ -299,14 +299,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
-    <t>COMPANY: VIJIM LIMITED
-ADD: 2/F,YAU TAK BUILDING,167 LOCKHART ROAD, WANCHAI,HONG
-KONG
-CONTACT: PENNY YU
-TEL: 86-133-1654-5525
-E-MAIL: CONTACT@ULANZI.COM</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -535,6 +527,96 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
+    <t>DESCRIPTION</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATERIAL</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>QUANTITY</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>PICTURE</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIT PRICE</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOTAL</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUBTOTAL</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIJIM LIMITED</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>BENEFICIARY ADDRESS :</t>
+  </si>
+  <si>
+    <t>2/F YAU TAK BUILDING,167 LOCKHART ROAD,WANCHAI HK</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>STANDARD CHARTERED BANK (HONG KONG) LTD</t>
+  </si>
+  <si>
+    <t>SCBLHKHH</t>
+  </si>
+  <si>
+    <t>32ND FLOOR, 4-4A DES VOEUX ROAD CENTRAL,HONG KONG SAR</t>
+  </si>
+  <si>
+    <t>BANK CODE :</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>BRANCH CODE :</t>
+  </si>
+  <si>
+    <t>COMPANY: VIJIM LIMITED
+ADD: 2/F,YAU TAK BUILDING,167 LOCKHART ROAD, WANCHAI,HONG
+KONG
+CONTACT: PENNY YU
+TEL: 86-133-1654-5525
+E-MAIL: CONTACT@ULANZI.COM</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{customerName}
+{address}
+{email}
+TEL : {telNumber}
+MOBILE : </t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.no}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.model}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{code}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>商业发票</t>
     </r>
@@ -570,122 +652,41 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>DATE: ${.billDate}</t>
+      <t>DATE: {billDate}</t>
     </r>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>${.code}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${.no}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${skuNo}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${model}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>DESCRIPTION</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATERIAL</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>QUANTITY</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${.qty}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>PICTURE</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNIT PRICE</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${.priceStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${.totalQty}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>TOTAL</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>SUBTOTAL</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${.amountStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${.shippingFeeStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${.totalFeeStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${totalAmountStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>${.collectionConditionStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">${.customerName}
-${.address}
-${.email}
-TEL : ${.telNumber}
-MOBILE : </t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>VIJIM LIMITED</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>BENEFICIARY ADDRESS :</t>
-  </si>
-  <si>
-    <t>2/F YAU TAK BUILDING,167 LOCKHART ROAD,WANCHAI HK</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>STANDARD CHARTERED BANK (HONG KONG) LTD</t>
-  </si>
-  <si>
-    <t>SCBLHKHH</t>
-  </si>
-  <si>
-    <t>32ND FLOOR, 4-4A DES VOEUX ROAD CENTRAL,HONG KONG SAR</t>
-  </si>
-  <si>
-    <t>BANK CODE :</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>BRANCH CODE :</t>
+    <t>{.qty}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.priceStr}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.amountStr}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{totalQty}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{totalAmountStr}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{shippingFeeStr}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{totalFeeStr}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>{receiveConditionStr}</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1077,6 +1078,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1110,50 +1138,23 @@
     <xf numFmtId="178" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -1572,84 +1573,84 @@
   <sheetData>
     <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="21"/>
-      <c r="G1" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="G1" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="A2" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
     </row>
     <row r="3" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-    </row>
-    <row r="4" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="47"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+    </row>
+    <row r="4" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="20" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
       <c r="K5" s="13"/>
     </row>
     <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
+      <c r="A6" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
       <c r="G6" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
@@ -1658,17 +1659,17 @@
       <c r="L6" s="15"/>
     </row>
     <row r="7" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="45"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
       <c r="G7" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="24"/>
@@ -1676,14 +1677,14 @@
       <c r="L7" s="15"/>
     </row>
     <row r="8" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="47"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
       <c r="G8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" s="22"/>
       <c r="I8" s="23"/>
@@ -1692,19 +1693,19 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="H9" s="22" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="24"/>
@@ -1713,7 +1714,7 @@
     </row>
     <row r="10" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
@@ -1721,283 +1722,283 @@
       <c r="E10" s="23"/>
       <c r="F10" s="23"/>
       <c r="G10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="22" t="s">
         <v>8</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>9</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="24"/>
       <c r="K10" s="13"/>
     </row>
     <row r="11" spans="1:12" ht="3.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="6" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="7"/>
       <c r="F13" s="8"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="38"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="42"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+    </row>
+    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="44"/>
+      <c r="C18" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="33"/>
+    </row>
+    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="44"/>
+      <c r="C19" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="33"/>
+    </row>
+    <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="32">
+        <v>47413304210</v>
+      </c>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="33"/>
+    </row>
+    <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="44"/>
+      <c r="C21" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="33"/>
+    </row>
+    <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="44"/>
+      <c r="C22" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="33"/>
+    </row>
+    <row r="23" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="44"/>
+      <c r="C23" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="11" t="s">
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="33"/>
+    </row>
+    <row r="24" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="B24" s="44"/>
+      <c r="C24" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="J14" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="33"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-    </row>
-    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="37"/>
-    </row>
-    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="37"/>
-    </row>
-    <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="36">
-        <v>47413304210</v>
-      </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="37"/>
-    </row>
-    <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="37"/>
-    </row>
-    <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="37"/>
-    </row>
-    <row r="23" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="37"/>
-    </row>
-    <row r="24" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="37"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="33"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="36">
+      <c r="A25" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="44"/>
+      <c r="C25" s="32">
         <v>474</v>
       </c>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="37"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="33"/>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="27" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="23" t="s">
         <v>22</v>
-      </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="23" t="s">
-        <v>23</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
@@ -2008,24 +2009,24 @@
       <c r="J27" s="24"/>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G28" s="38" t="s">
+      <c r="G28" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="50"/>
+      <c r="I28" s="12"/>
+    </row>
+    <row r="29" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G29" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="39"/>
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G29" s="40" t="s">
+      <c r="H29" s="46"/>
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="G30" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="41"/>
-      <c r="I29" s="12"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="G30" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="41"/>
+      <c r="H30" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="38">
@@ -2038,35 +2039,35 @@
     <mergeCell ref="C27:J27"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G1:J5"/>
-    <mergeCell ref="A6:F8"/>
-    <mergeCell ref="A2:F4"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:J22"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:J19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C20:J20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:J21"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="C18:J18"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G1:J5"/>
+    <mergeCell ref="A6:F8"/>
+    <mergeCell ref="A2:F4"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.27500000000000002" right="0.118055555555556" top="0.156944444444444" bottom="0.118055555555556" header="0.196527777777778" footer="0.156944444444444"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SalesContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SalesContract.xlsx
@@ -299,39 +299,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>RECEIVER :[</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客户资料，公司，地址，邮箱，电话，手机号</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>PO NO. :</t>
   </si>
   <si>
@@ -339,71 +306,6 @@
   </si>
   <si>
     <t>TRADE TERM :</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>TRSANSPORT DETAILS:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>BY Air/</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>其他待定】【无法取值</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>固定】</t>
-    </r>
   </si>
   <si>
     <t>PAYMENT TERM :</t>
@@ -510,60 +412,43 @@
     <t>DATE:  2023/4/18</t>
   </si>
   <si>
-    <r>
-      <t>ISSUER :</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【固定】</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
     <t>DESCRIPTION</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>MATERIAL</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>QUANTITY</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>PICTURE</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>UNIT PRICE</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>TOTAL</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>SUBTOTAL</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>VIJIM LIMITED</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>BENEFICIARY ADDRESS :</t>
   </si>
   <si>
     <t>2/F YAU TAK BUILDING,167 LOCKHART ROAD,WANCHAI HK</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>STANDARD CHARTERED BANK (HONG KONG) LTD</t>
@@ -590,7 +475,7 @@
 CONTACT: PENNY YU
 TEL: 86-133-1654-5525
 E-MAIL: CONTACT@ULANZI.COM</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">{customerName}
@@ -598,23 +483,23 @@
 {email}
 TEL : {telNumber}
 MOBILE : </t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.no}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.skuNo}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.model}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{code}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -654,39 +539,51 @@
       </rPr>
       <t>DATE: {billDate}</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.qty}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.priceStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.amountStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{totalQty}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{totalAmountStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{shippingFeeStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{totalFeeStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{receiveConditionStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>ISSUER :</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>RECEIVER :</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRSANSPORT DETAILS:</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -698,7 +595,7 @@
     <numFmt numFmtId="177" formatCode="General&quot;  Pcs&quot;"/>
     <numFmt numFmtId="178" formatCode="\$#,##0.00;\-\$#,##0.00"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -798,14 +695,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FF1FA8F7"/>
       <name val="宋体"/>
@@ -828,7 +717,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,12 +727,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1002,7 +885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1018,9 +901,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1045,15 +925,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1063,21 +937,81 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1099,65 +1033,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1572,464 +1449,491 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="A1" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A2" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
+      <c r="A2" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
     </row>
     <row r="5" spans="1:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="13"/>
-    </row>
-    <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="33"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="13"/>
+    </row>
+    <row r="7" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="45"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="15"/>
-    </row>
-    <row r="7" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13"/>
+    </row>
+    <row r="8" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="15"/>
-    </row>
-    <row r="8" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="30"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="33"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="14"/>
+    </row>
+    <row r="9" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="34" t="s">
+      <c r="H9" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13"/>
+    </row>
+    <row r="10" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="1" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="15"/>
-    </row>
-    <row r="10" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="22" t="s">
+      <c r="H10" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="13"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:12" ht="3.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="H14" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+    </row>
+    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="22"/>
+    </row>
+    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="38"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="41" t="s">
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+    </row>
+    <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="42"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-    </row>
-    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="43" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="21">
+        <v>47413304210</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="32" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="33"/>
-    </row>
-    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="43" t="s">
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
+    </row>
+    <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="32" t="s">
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="22"/>
+    </row>
+    <row r="23" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="33"/>
-    </row>
-    <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="32">
-        <v>47413304210</v>
-      </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33"/>
-    </row>
-    <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="32" t="s">
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="22"/>
+    </row>
+    <row r="24" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="33"/>
-    </row>
-    <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="32" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33"/>
-    </row>
-    <row r="23" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="32" t="s">
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="22"/>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="33"/>
-    </row>
-    <row r="24" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="44"/>
-      <c r="C24" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="33"/>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="32">
+      <c r="B25" s="20"/>
+      <c r="C25" s="21">
         <v>474</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="33"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="27" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="26"/>
+    </row>
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G28" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="23" t="s">
+      <c r="H28" s="28"/>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G29" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="24"/>
-    </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G28" s="49" t="s">
+      <c r="H29" s="18"/>
+      <c r="I29" s="11"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="G30" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="50"/>
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G29" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="46"/>
-      <c r="I29" s="12"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="G30" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" s="46"/>
+      <c r="H30" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G1:J5"/>
+    <mergeCell ref="A6:F8"/>
+    <mergeCell ref="A2:F4"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:J23"/>
@@ -2041,35 +1945,8 @@
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C24:J24"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="G1:J5"/>
-    <mergeCell ref="A6:F8"/>
-    <mergeCell ref="A2:F4"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.27500000000000002" right="0.118055555555556" top="0.156944444444444" bottom="0.118055555555556" header="0.196527777777778" footer="0.156944444444444"/>
   <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SalesContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SalesContract.xlsx
@@ -299,39 +299,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>RECEIVER :[</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客户资料，公司，地址，邮箱，电话，手机号</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>PO NO. :</t>
   </si>
   <si>
@@ -339,71 +306,6 @@
   </si>
   <si>
     <t>TRADE TERM :</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>TRSANSPORT DETAILS:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>BY Air/</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>其他待定】【无法取值</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>固定】</t>
-    </r>
   </si>
   <si>
     <t>PAYMENT TERM :</t>
@@ -510,60 +412,43 @@
     <t>DATE:  2023/4/18</t>
   </si>
   <si>
-    <r>
-      <t>ISSUER :</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【固定】</t>
-    </r>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
     <t>DESCRIPTION</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>MATERIAL</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>QUANTITY</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>PICTURE</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>UNIT PRICE</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>TOTAL</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>SUBTOTAL</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>VIJIM LIMITED</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>BENEFICIARY ADDRESS :</t>
   </si>
   <si>
     <t>2/F YAU TAK BUILDING,167 LOCKHART ROAD,WANCHAI HK</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>STANDARD CHARTERED BANK (HONG KONG) LTD</t>
@@ -590,7 +475,7 @@
 CONTACT: PENNY YU
 TEL: 86-133-1654-5525
 E-MAIL: CONTACT@ULANZI.COM</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">{customerName}
@@ -598,23 +483,23 @@
 {email}
 TEL : {telNumber}
 MOBILE : </t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.no}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.skuNo}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.model}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{code}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -654,39 +539,51 @@
       </rPr>
       <t>DATE: {billDate}</t>
     </r>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.qty}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.priceStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{.amountStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{totalQty}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{totalAmountStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{shippingFeeStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{totalFeeStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>{receiveConditionStr}</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>ISSUER :</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>RECEIVER :</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRSANSPORT DETAILS:</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -698,7 +595,7 @@
     <numFmt numFmtId="177" formatCode="General&quot;  Pcs&quot;"/>
     <numFmt numFmtId="178" formatCode="\$#,##0.00;\-\$#,##0.00"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -798,14 +695,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FF1FA8F7"/>
       <name val="宋体"/>
@@ -828,7 +717,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,12 +727,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1002,7 +885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1018,9 +901,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1045,15 +925,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1063,21 +937,81 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1099,65 +1033,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1572,464 +1449,491 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="A1" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A2" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
+      <c r="A2" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
     </row>
     <row r="5" spans="1:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="13"/>
-    </row>
-    <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="33"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="13"/>
+    </row>
+    <row r="7" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="45"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="15"/>
-    </row>
-    <row r="7" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13"/>
+    </row>
+    <row r="8" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="15"/>
-    </row>
-    <row r="8" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="30"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="33"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="14"/>
+    </row>
+    <row r="9" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="34" t="s">
+      <c r="H9" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13"/>
+    </row>
+    <row r="10" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="1" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="15"/>
-    </row>
-    <row r="10" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="22" t="s">
+      <c r="H10" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="13"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:12" ht="3.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="H14" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+    </row>
+    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="22"/>
+    </row>
+    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="38"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="41" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="41" t="s">
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="22"/>
+    </row>
+    <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="42"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-    </row>
-    <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="43" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="21">
+        <v>47413304210</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="32" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="33"/>
-    </row>
-    <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="43" t="s">
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
+    </row>
+    <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="32" t="s">
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="22"/>
+    </row>
+    <row r="23" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="33"/>
-    </row>
-    <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="32">
-        <v>47413304210</v>
-      </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33"/>
-    </row>
-    <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="32" t="s">
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="22"/>
+    </row>
+    <row r="24" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="33"/>
-    </row>
-    <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="32" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33"/>
-    </row>
-    <row r="23" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="32" t="s">
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="22"/>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="33"/>
-    </row>
-    <row r="24" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="44"/>
-      <c r="C24" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="33"/>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="32">
+      <c r="B25" s="20"/>
+      <c r="C25" s="21">
         <v>474</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="33"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="27" spans="1:10" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="26"/>
+    </row>
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G28" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="23" t="s">
+      <c r="H28" s="28"/>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G29" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="24"/>
-    </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G28" s="49" t="s">
+      <c r="H29" s="18"/>
+      <c r="I29" s="11"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="G30" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="50"/>
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G29" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="46"/>
-      <c r="I29" s="12"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="G30" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" s="46"/>
+      <c r="H30" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G1:J5"/>
+    <mergeCell ref="A6:F8"/>
+    <mergeCell ref="A2:F4"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:J21"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:J23"/>
@@ -2041,35 +1945,8 @@
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C24:J24"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="G1:J5"/>
-    <mergeCell ref="A6:F8"/>
-    <mergeCell ref="A2:F4"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.27500000000000002" right="0.118055555555556" top="0.156944444444444" bottom="0.118055555555556" header="0.196527777777778" footer="0.156944444444444"/>
   <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SalesContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SalesContract.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>ISSUER :</t>
   </si>
@@ -156,6 +156,9 @@
     <t>{.model}</t>
   </si>
   <si>
+    <t>{.desc}</t>
+  </si>
+  <si>
     <t>{.qty}</t>
   </si>
   <si>
@@ -294,8 +297,8 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="\$#,##0.00;\-\$#,##0.00"/>
-    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="\$#,##0.00;\-\$#,##0.00"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -1260,7 +1263,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1284,10 +1287,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1326,7 +1329,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2013,18 +2016,26 @@
       <c r="C13" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="24"/>
+      <c r="D13" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>28</v>
+      </c>
       <c r="H13" s="25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I13" s="47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J13" s="47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" ht="39" customHeight="1" spans="1:10">
@@ -2035,21 +2046,21 @@
       <c r="E14" s="27"/>
       <c r="F14" s="28"/>
       <c r="G14" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H14" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J14" s="48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1" spans="1:10">
       <c r="A15" s="30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -2060,12 +2071,12 @@
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
       <c r="J15" s="47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:10">
       <c r="A16" s="30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="30"/>
       <c r="C16" s="30"/>
@@ -2076,7 +2087,7 @@
       <c r="H16" s="30"/>
       <c r="I16" s="30"/>
       <c r="J16" s="47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="27.75" customHeight="1" spans="1:10">
@@ -2093,11 +2104,11 @@
     </row>
     <row r="18" ht="24.95" customHeight="1" spans="1:10">
       <c r="A18" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="34"/>
       <c r="C18" s="35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" s="35"/>
       <c r="E18" s="35"/>
@@ -2109,11 +2120,11 @@
     </row>
     <row r="19" ht="24.95" customHeight="1" spans="1:10">
       <c r="A19" s="33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="34"/>
       <c r="C19" s="35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" s="35"/>
       <c r="E19" s="35"/>
@@ -2125,7 +2136,7 @@
     </row>
     <row r="20" ht="24.95" customHeight="1" spans="1:10">
       <c r="A20" s="33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="34"/>
       <c r="C20" s="35">
@@ -2141,11 +2152,11 @@
     </row>
     <row r="21" ht="24.95" customHeight="1" spans="1:10">
       <c r="A21" s="33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" s="34"/>
       <c r="C21" s="35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D21" s="35"/>
       <c r="E21" s="35"/>
@@ -2157,11 +2168,11 @@
     </row>
     <row r="22" ht="24.95" customHeight="1" spans="1:10">
       <c r="A22" s="33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" s="34"/>
       <c r="C22" s="35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" s="35"/>
       <c r="E22" s="35"/>
@@ -2173,11 +2184,11 @@
     </row>
     <row r="23" ht="26.25" customHeight="1" spans="1:10">
       <c r="A23" s="33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="34"/>
       <c r="C23" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" s="35"/>
       <c r="E23" s="35"/>
@@ -2189,11 +2200,11 @@
     </row>
     <row r="24" ht="24.95" customHeight="1" spans="1:10">
       <c r="A24" s="33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="34"/>
       <c r="C24" s="51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24" s="35"/>
       <c r="E24" s="35"/>
@@ -2205,7 +2216,7 @@
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:10">
       <c r="A25" s="33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="34"/>
       <c r="C25" s="35">
@@ -2222,11 +2233,11 @@
     <row r="26" ht="14.25" customHeight="1"/>
     <row r="27" ht="55.5" customHeight="1" spans="1:10">
       <c r="A27" s="36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B27" s="37"/>
       <c r="C27" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
@@ -2238,21 +2249,21 @@
     </row>
     <row r="28" ht="18" customHeight="1" spans="7:9">
       <c r="G28" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H28" s="39"/>
       <c r="I28" s="41"/>
     </row>
     <row r="29" ht="23.1" customHeight="1" spans="7:9">
       <c r="G29" s="40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H29" s="41"/>
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="7:8">
       <c r="G30" s="40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H30" s="41"/>
     </row>
